--- a/workbooks/09 Formulas 5 - Text.xlsx
+++ b/workbooks/09 Formulas 5 - Text.xlsx
@@ -677,10 +677,10 @@
     <t>LEFT + FIND</t>
   </si>
   <si>
+    <t>(…)*(…)</t>
+  </si>
+  <si>
     <t>return 2+ columns</t>
-  </si>
-  <si>
-    <t>=</t>
   </si>
   <si>
     <t>T5</t>
@@ -1728,7 +1728,7 @@
     <t>"text"</t>
   </si>
   <si>
-    <t>"&gt;="&amp;K6</t>
+    <t>SORT(UNIQUE(…))</t>
   </si>
   <si>
     <t>Which function supplies the cut position inside =LEFT(A2, ____("@",A2)-1)?</t>

--- a/workbooks/09 Formulas 5 - Text.xlsx
+++ b/workbooks/09 Formulas 5 - Text.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="703">
   <si>
     <t>Challenge</t>
   </si>
@@ -1731,49 +1731,52 @@
     <t>SORT(UNIQUE(…))</t>
   </si>
   <si>
+    <t>Which move is this? =LEFT(A2,FIND("@",A2)-1) takes everything before the @.</t>
+  </si>
+  <si>
+    <t>▶ Open F5-3 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F5-3 Find the Gem C1</t>
+  </si>
+  <si>
+    <t>=FIND</t>
+  </si>
+  <si>
+    <t>=FIND(</t>
+  </si>
+  <si>
+    <t>=FIND()</t>
+  </si>
+  <si>
+    <t>FIND(</t>
+  </si>
+  <si>
+    <t>FIND()</t>
+  </si>
+  <si>
+    <t>F5-3 Find the Gem C2</t>
+  </si>
+  <si>
+    <t>=SEARCH</t>
+  </si>
+  <si>
+    <t>=SEARCH(</t>
+  </si>
+  <si>
+    <t>=SEARCH()</t>
+  </si>
+  <si>
+    <t>SEARCH(</t>
+  </si>
+  <si>
+    <t>SEARCH()</t>
+  </si>
+  <si>
+    <t>F5-3 Find the Gem C3</t>
+  </si>
+  <si>
     <t>Which function supplies the cut position inside =LEFT(A2, ____("@",A2)-1)?</t>
-  </si>
-  <si>
-    <t>▶ Open F5-3 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F5-3 Find the Gem C1</t>
-  </si>
-  <si>
-    <t>=FIND</t>
-  </si>
-  <si>
-    <t>=FIND(</t>
-  </si>
-  <si>
-    <t>=FIND()</t>
-  </si>
-  <si>
-    <t>FIND(</t>
-  </si>
-  <si>
-    <t>FIND()</t>
-  </si>
-  <si>
-    <t>F5-3 Find the Gem C2</t>
-  </si>
-  <si>
-    <t>=SEARCH</t>
-  </si>
-  <si>
-    <t>=SEARCH(</t>
-  </si>
-  <si>
-    <t>=SEARCH()</t>
-  </si>
-  <si>
-    <t>SEARCH(</t>
-  </si>
-  <si>
-    <t>SEARCH()</t>
-  </si>
-  <si>
-    <t>F5-3 Find the Gem C3</t>
   </si>
   <si>
     <t>F5-3 Find the Gem C4</t>
@@ -3363,7 +3366,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3373,12 +3376,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3388,32 +3391,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3423,30 +3426,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F5-1 Cut &amp; Splice'!$G$15:$G$46)&amp;" / 250"</f>
@@ -3461,15 +3464,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F5-2 Clean Up'!$G$15:$G$46)&amp;" / 250"</f>
@@ -3484,15 +3487,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F5-3 Find the Gem'!$G$13:$G$39)&amp;" / 200"</f>
@@ -3507,15 +3510,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F5-4 Assemble'!$G$13:$G$39)&amp;" / 200"</f>
@@ -3530,15 +3533,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3553,12 +3556,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">(SUM('F5-1 Cut &amp; Splice'!$G$15:$G$46)+SUM('F5-2 Clean Up'!$G$15:$G$46)+SUM('F5-3 Find the Gem'!$G$13:$G$39)+SUM('F5-4 Assemble'!$G$13:$G$39)+SUM(Boss!$G$14:$G$33))&amp;" / 1060"</f>
@@ -3567,19 +3570,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">_xlfn.LET(_xlpm.p,(SUM('F5-1 Cut &amp; Splice'!$G$15:$G$46)+SUM('F5-2 Clean Up'!$G$15:$G$46)+SUM('F5-3 Find the Gem'!$G$13:$G$39)+SUM('F5-4 Assemble'!$G$13:$G$39)+SUM(Boss!$G$14:$G$33))/1060,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3588,7 +3591,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IFERROR(INDEX($A$13:$A$16,MATCH("☆☆☆",$D$13:$D$16,0))&amp;" "&amp;INDEX($B$13:$B$16,MATCH("☆☆☆",$D$13:$D$16,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3597,7 +3600,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="13" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -3634,7 +3637,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3645,7 +3648,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -3664,7 +3667,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -3675,19 +3678,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C6" s="30"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C8" s="31" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -3696,7 +3699,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C9" s="31">
         <v>15</v>
@@ -3704,7 +3707,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('F5-1 Cut &amp; Splice'!$G$15:$G$46)&gt;=250*0.5,SUM('F5-2 Clean Up'!$G$15:$G$46)&gt;=250*0.5,SUM('F5-3 Find the Gem'!$G$13:$G$39)&gt;=200*0.5,SUM('F5-4 Assemble'!$G$13:$G$39)&gt;=200*0.5),"OPEN","LOCKED")</f>
@@ -3717,7 +3720,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3751,7 +3754,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B14" s="32" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which function joins a range of text with a delimiter?  (from F5-4 Assemble)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3774,7 +3777,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B15" s="32" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","Which function turns a number or date into formatted text?  (from F5-4 Assemble)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3797,7 +3800,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B16" s="32" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","Which function turns text that looks like a number into a number?  (from F5-4 Assemble)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3820,7 +3823,7 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B17" s="32" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","Which function returns characters from the start of a text?  (from F5-1 Cut &amp; Splice)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3843,7 +3846,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B18" s="32" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","Which function returns characters from the end of a text?  (from F5-1 Cut &amp; Splice)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3866,7 +3869,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B19" s="32" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","Which function returns characters from the middle of a text?  (from F5-1 Cut &amp; Splice)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3889,7 +3892,7 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B20" s="32" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which function counts the characters in a text?  (from F5-1 Cut &amp; Splice)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3912,7 +3915,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B21" s="32" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which character joins pieces of text in a formula?  (from F5-1 Cut &amp; Splice)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3935,7 +3938,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -3946,7 +3949,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3974,14 +3977,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B26" s="32" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In D6 tidy B6: no extra spaces, each word capitalized.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$6),EXACT('Boss Arena'!$D$6,Key!$C$100)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"PROPER"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TRIM"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use PROPER and TRIM"))))),"LOCKED")</f>
@@ -3999,14 +4002,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B27" s="32" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In D7 return the 4 digits in the middle of B7 (they start at character 4).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$7),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$7),'Boss Arena'!$D$7=Key!$C$101),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MID"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use MID"))))),"LOCKED")</f>
@@ -4024,14 +4027,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B28" s="32" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In D8 return the username in B8 (everything before ""@"").","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$8),EXACT('Boss Arena'!$D$8,Key!$C$102)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"LEFT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$8))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use LEFT and FIND"))))),"LOCKED")</f>
@@ -4049,14 +4052,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B29" s="32" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In D9 return the last name from B9 (after the space).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$9),EXACT('Boss Arena'!$D$9,Key!$C$103)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MID"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use MID and FIND"))))),"LOCKED")</f>
@@ -4074,14 +4077,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B30" s="32" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In D10 replace every ""/"" in B10 with ""-"".","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$10),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$10),'Boss Arena'!$D$10=Key!$C$104),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUBSTITUTE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$10)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUBSTITUTE"))))),"LOCKED")</f>
@@ -4099,14 +4102,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B31" s="32" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In D11 turn the text in B11 into a number.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$11),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$11)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$11),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$11),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$11),ABS('Boss Arena'!$D$11-Key!$C$105)&lt;=1E-9*MAX(1,ABS(Key!$C$105))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VALUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$11)))))),"✔ CLEAR","✘ CLOSE · right value, but use VALUE"))))),"LOCKED")</f>
@@ -4124,14 +4127,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B32" s="32" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In D12 show the date in B12 as text like 04/07/2026 (format ""dd/mm/yyyy"").","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$12),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$12),'Boss Arena'!$D$12=Key!$C$106),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TEXT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$12)))))),"✔ CLEAR","✘ CLOSE · right value, but use TEXT"))))),"LOCKED")</f>
@@ -4149,14 +4152,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B33" s="32" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In D13 join the tags in B15:B18 with "" | "", skipping the blank.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$13),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$13)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$13),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$13),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$13),EXACT('Boss Arena'!$D$13,Key!$C$107)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TEXTJOIN"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$13)))))),"✔ CLEAR","✘ CLOSE · right value, but use TEXTJOIN"))))),"LOCKED")</f>
@@ -4275,7 +4278,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4288,15 +4291,15 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="27" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>11</v>
@@ -4304,34 +4307,34 @@
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D6" s="28"/>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="5" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D7" s="28"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>356</v>
@@ -4340,19 +4343,19 @@
     </row>
     <row r="10" spans="1:4">
       <c r="B10" s="5" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D10" s="28"/>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D11" s="28"/>
     </row>
@@ -4361,34 +4364,34 @@
         <v>46207</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D12" s="28"/>
     </row>
     <row r="13" spans="1:4">
       <c r="C13" s="5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D13" s="28"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="5" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -4416,7 +4419,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4424,245 +4427,245 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.75" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.75" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.75" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>39</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>142</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.75" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>135</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.75" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>143</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.75" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>233</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>136</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>129</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>141</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>152</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>130</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>148</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
@@ -6092,10 +6095,10 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B68" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C68" cm="1">
         <f t="array" ref="C68">FIND("@",'F5-3 Arena'!$B$6)</f>
@@ -6104,10 +6107,10 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B69" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C69" cm="1">
         <f t="array" ref="C69">SEARCH("ARCADE",'F5-3 Arena'!$B$6)</f>
@@ -6116,10 +6119,10 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B70" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C70" cm="1" t="str">
         <f t="array" ref="C70">LEFT('F5-3 Arena'!$B$6,FIND("@",'F5-3 Arena'!$B$6)-1)</f>
@@ -6128,10 +6131,10 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B71" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C71" cm="1" t="str">
         <f t="array" ref="C71">MID('F5-3 Arena'!$B$7,FIND(" ",'F5-3 Arena'!$B$7)+1,100)</f>
@@ -6140,7 +6143,7 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B72" t="s">
         <v>411</v>
@@ -6166,7 +6169,7 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s">
         <v>414</v>
@@ -6192,7 +6195,7 @@
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s">
         <v>264</v>
@@ -6203,87 +6206,87 @@
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B75" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E75" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B76" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E76" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B77" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E77" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B78" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E78" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B79" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E79" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B80" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E80" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B81" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E81" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B82" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C82" t="s">
         <v>130</v>
@@ -6292,7 +6295,7 @@
         <v>143</v>
       </c>
       <c r="F82" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G82" t="s">
         <v>130</v>
@@ -6303,10 +6306,10 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B83" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C83" t="s">
         <v>148</v>
@@ -6326,13 +6329,13 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B84" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C84" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E84" t="s">
         <v>233</v>
@@ -6344,93 +6347,93 @@
         <v>148</v>
       </c>
       <c r="H84" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B85" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E85" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F85" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G85" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H85" t="s">
         <v>130</v>
       </c>
       <c r="I85" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J85" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B86" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E86" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F86" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G86" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H86" t="s">
         <v>148</v>
       </c>
       <c r="I86" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J86" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B87" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E87" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F87" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G87" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H87" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I87" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J87" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B88" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C88" cm="1" t="str">
         <f t="array" ref="C88">_xlfn.TEXTJOIN(", ",TRUE,'F5-4 Arena'!$B$6:$B$10)</f>
@@ -6439,10 +6442,10 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B89" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C89" cm="1" t="str">
         <f t="array" ref="C89">TEXT('F5-4 Arena'!$B$12,"yyyy-mm-dd")</f>
@@ -6451,10 +6454,10 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B90" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C90" cm="1">
         <f t="array" ref="C90">VALUE('F5-4 Arena'!$B$14)</f>
@@ -6463,10 +6466,10 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B91" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C91" cm="1" t="str">
         <f t="array" ref="C91">"Total: "&amp;TEXT('F5-4 Arena'!$B$16,"$#,##0.00")</f>
@@ -6475,85 +6478,85 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B92" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E92" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F92" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G92" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H92" t="s">
         <v>130</v>
       </c>
       <c r="I92" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J92" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B93" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E93" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F93" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G93" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H93" t="s">
         <v>148</v>
       </c>
       <c r="I93" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J93" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B94" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E94" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F94" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G94" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H94" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I94" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J94" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B95" t="s">
         <v>128</v>
@@ -6579,7 +6582,7 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B96" t="s">
         <v>134</v>
@@ -6605,7 +6608,7 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B97" t="s">
         <v>140</v>
@@ -6631,7 +6634,7 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B98" t="s">
         <v>147</v>
@@ -6657,7 +6660,7 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B99" t="s">
         <v>103</v>
@@ -6671,10 +6674,10 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B100" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C100" cm="1" t="str">
         <f t="array" ref="C100">PROPER(TRIM('Boss Arena'!$B$6))</f>
@@ -6683,10 +6686,10 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B101" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C101" cm="1">
         <f t="array" ref="C101">MID('Boss Arena'!$B$7,4,4)</f>
@@ -6695,10 +6698,10 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B102" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C102" cm="1" t="str">
         <f t="array" ref="C102">LEFT('Boss Arena'!$B$8,FIND("@",'Boss Arena'!$B$8)-1)</f>
@@ -6707,10 +6710,10 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B103" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C103" cm="1" t="str">
         <f t="array" ref="C103">MID('Boss Arena'!$B$9,FIND(" ",'Boss Arena'!$B$9)+1,100)</f>
@@ -6719,10 +6722,10 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B104" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C104" cm="1" t="str">
         <f t="array" ref="C104">SUBSTITUTE('Boss Arena'!$B$10,"/","-")</f>
@@ -6731,10 +6734,10 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B105" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C105" cm="1">
         <f t="array" ref="C105">VALUE('Boss Arena'!$B$11)</f>
@@ -6743,10 +6746,10 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B106" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C106" cm="1" t="str">
         <f t="array" ref="C106">TEXT('Boss Arena'!$B$12,"dd/mm/yyyy")</f>
@@ -6755,10 +6758,10 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B107" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C107" cm="1" t="str">
         <f t="array" ref="C107">_xlfn.TEXTJOIN(" | ",TRUE,'Boss Arena'!$B$15:$B$18)</f>
@@ -8843,7 +8846,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8854,7 +8857,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9376,7 +9379,7 @@
         <v>179</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -9398,10 +9401,10 @@
         <v>186</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F5-3 Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('F5-3 Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-3 Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-3 Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F5-3 Arena'!$D$6),ABS('F5-3 Arena'!$D$6-Key!$C$68)&lt;=1E-9*MAX(1,ABS(Key!$C$68))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use FIND")))))</f>
@@ -9422,10 +9425,10 @@
         <v>188</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F5-3 Arena'!$D$7),"",IF(NOT(_xlfn.ISFORMULA('F5-3 Arena'!$D$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-3 Arena'!$D$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-3 Arena'!$D$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F5-3 Arena'!$D$7),ABS('F5-3 Arena'!$D$7-Key!$C$69)&lt;=1E-9*MAX(1,ABS(Key!$C$69))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SEARCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use SEARCH")))))</f>
@@ -9446,10 +9449,10 @@
         <v>191</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F5-3 Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('F5-3 Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-3 Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-3 Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-3 Arena'!$D$8),EXACT('F5-3 Arena'!$D$8,Key!$C$70)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"LEFT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$8))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use LEFT and FIND")))))</f>
@@ -9470,10 +9473,10 @@
         <v>196</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F5-3 Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('F5-3 Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-3 Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-3 Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-3 Arena'!$D$9),EXACT('F5-3 Arena'!$D$9,Key!$C$71)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MID"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use MID and FIND")))))</f>
@@ -9697,7 +9700,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9708,7 +9711,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9760,7 +9763,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>130</v>
@@ -9771,7 +9774,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>148</v>
@@ -9782,10 +9785,10 @@
         <v>31</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22" customHeight="1">
@@ -9827,7 +9830,7 @@
         <v>54</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -9849,7 +9852,7 @@
         <v>60</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -9871,7 +9874,7 @@
         <v>70</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -9893,7 +9896,7 @@
         <v>80</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -9915,7 +9918,7 @@
         <v>90</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -9937,7 +9940,7 @@
         <v>100</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -9959,7 +9962,7 @@
         <v>105</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -9981,7 +9984,7 @@
         <v>110</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -10003,7 +10006,7 @@
         <v>119</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -10025,7 +10028,7 @@
         <v>124</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -10081,7 +10084,7 @@
         <v>131</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -10103,7 +10106,7 @@
         <v>137</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -10125,7 +10128,7 @@
         <v>144</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -10155,7 +10158,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -10186,7 +10189,7 @@
         <v>165</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -10208,7 +10211,7 @@
         <v>172</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -10230,7 +10233,7 @@
         <v>179</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -10252,10 +10255,10 @@
         <v>186</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F5-4 Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('F5-4 Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-4 Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-4 Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-4 Arena'!$D$6),EXACT('F5-4 Arena'!$D$6,Key!$C$88)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TEXTJOIN"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-4 Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use TEXTJOIN")))))</f>
@@ -10276,10 +10279,10 @@
         <v>188</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F5-4 Arena'!$D$12),"",IF(NOT(_xlfn.ISFORMULA('F5-4 Arena'!$D$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-4 Arena'!$D$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-4 Arena'!$D$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-4 Arena'!$D$12),'F5-4 Arena'!$D$12=Key!$C$89),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TEXT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-4 Arena'!$D$12)))))),"✔ CLEAR","✘ CLOSE · right value, but use TEXT")))))</f>
@@ -10300,10 +10303,10 @@
         <v>191</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F5-4 Arena'!$D$14),"",IF(NOT(_xlfn.ISFORMULA('F5-4 Arena'!$D$14)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-4 Arena'!$D$14),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-4 Arena'!$D$14),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F5-4 Arena'!$D$14),ABS('F5-4 Arena'!$D$14-Key!$C$90)&lt;=1E-9*MAX(1,ABS(Key!$C$90))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VALUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-4 Arena'!$D$14)))))),"✔ CLEAR","✘ CLOSE · right value, but use VALUE")))))</f>
@@ -10324,10 +10327,10 @@
         <v>196</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F5-4 Arena'!$D$16),"",IF(NOT(_xlfn.ISFORMULA('F5-4 Arena'!$D$16)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-4 Arena'!$D$16),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-4 Arena'!$D$16),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-4 Arena'!$D$16),EXACT('F5-4 Arena'!$D$16,Key!$C$91)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TEXT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-4 Arena'!$D$16)))))),"✔ CLEAR","✘ CLOSE · right value, but use TEXT")))))</f>
@@ -10465,7 +10468,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -10478,15 +10481,15 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="27" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>11</v>
@@ -10494,31 +10497,31 @@
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D6" s="28"/>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="B10" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -10526,27 +10529,27 @@
         <v>46096</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D12" s="28"/>
     </row>
     <row r="13" spans="1:4">
       <c r="B13" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D14" s="28"/>
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -10554,7 +10557,7 @@
         <v>1234.5</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D16" s="28"/>
     </row>

--- a/workbooks/09 Formulas 5 - Text.xlsx
+++ b/workbooks/09 Formulas 5 - Text.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="708">
   <si>
     <t>Challenge</t>
   </si>
@@ -395,7 +395,22 @@
     <t>0</t>
   </si>
   <si>
+    <t>=FALSE</t>
+  </si>
+  <si>
+    <t>=FALSE(</t>
+  </si>
+  <si>
+    <t>=FALSE()</t>
+  </si>
+  <si>
     <t>FALSE</t>
+  </si>
+  <si>
+    <t>FALSE(</t>
+  </si>
+  <si>
+    <t>FALSE()</t>
   </si>
   <si>
     <t>W2</t>
@@ -1173,6 +1188,24 @@
     <t>The position finder.</t>
   </si>
   <si>
+    <t>=XMATCH</t>
+  </si>
+  <si>
+    <t>=XMATCH(</t>
+  </si>
+  <si>
+    <t>=XMATCH()</t>
+  </si>
+  <si>
+    <t>XMATCH</t>
+  </si>
+  <si>
+    <t>XMATCH(</t>
+  </si>
+  <si>
+    <t>XMATCH()</t>
+  </si>
+  <si>
     <t>Which function goes inside INDEX to find the row position?  (from F4-4 Power Couple)</t>
   </si>
   <si>
@@ -1180,24 +1213,6 @@
   </si>
   <si>
     <t>X plus MATCH.</t>
-  </si>
-  <si>
-    <t>=XMATCH</t>
-  </si>
-  <si>
-    <t>=XMATCH(</t>
-  </si>
-  <si>
-    <t>=XMATCH()</t>
-  </si>
-  <si>
-    <t>XMATCH</t>
-  </si>
-  <si>
-    <t>XMATCH(</t>
-  </si>
-  <si>
-    <t>XMATCH()</t>
   </si>
   <si>
     <t>Which modern function returns a position with an exact match by default?  (from F4-4 Power Couple)</t>
@@ -2568,7 +2583,7 @@
     <t>NEXT UP</t>
   </si>
   <si>
-    <t>Replay a stage: select its yellow answer cells and press Delete. Undo an arena drill with Ctrl+Z.</t>
+    <t>Replay a stage: select a run of its yellow cells (Ctrl+click to add more), then press Delete. Undo an arena drill with Ctrl+Z.</t>
   </si>
   <si>
     <t>CHEAT CODES ▸ TEXT</t>
@@ -3366,7 +3381,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3376,12 +3391,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3391,32 +3406,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3426,30 +3441,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F5-1 Cut &amp; Splice'!$G$15:$G$46)&amp;" / 250"</f>
@@ -3464,15 +3479,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F5-2 Clean Up'!$G$15:$G$46)&amp;" / 250"</f>
@@ -3487,15 +3502,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F5-3 Find the Gem'!$G$13:$G$39)&amp;" / 200"</f>
@@ -3510,15 +3525,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F5-4 Assemble'!$G$13:$G$39)&amp;" / 200"</f>
@@ -3533,15 +3548,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3556,12 +3571,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="7" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">(SUM('F5-1 Cut &amp; Splice'!$G$15:$G$46)+SUM('F5-2 Clean Up'!$G$15:$G$46)+SUM('F5-3 Find the Gem'!$G$13:$G$39)+SUM('F5-4 Assemble'!$G$13:$G$39)+SUM(Boss!$G$14:$G$33))&amp;" / 1060"</f>
@@ -3570,19 +3585,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">_xlfn.LET(_xlpm.p,(SUM('F5-1 Cut &amp; Splice'!$G$15:$G$46)+SUM('F5-2 Clean Up'!$G$15:$G$46)+SUM('F5-3 Find the Gem'!$G$13:$G$39)+SUM('F5-4 Assemble'!$G$13:$G$39)+SUM(Boss!$G$14:$G$33))/1060,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3591,16 +3606,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
-        <f t="array" ref="B22">IFERROR(INDEX($A$13:$A$16,MATCH("☆☆☆",$D$13:$D$16,0))&amp;" "&amp;INDEX($B$13:$B$16,MATCH("☆☆☆",$D$13:$D$16,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
+        <f t="array" ref="B22">IFERROR(INDEX($A$13:$A$16,MATCH("☆☆☆",$D$13:$D$16,0))&amp;" "&amp;INDEX($B$13:$B$16,MATCH("☆☆☆",$D$13:$D$16,0)),IF(Start!$E$17="DEFEATED","All clear! Aim for rank S","the Boss"))</f>
         <v>F5-1 Cut &amp; Splice</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="13" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
   </sheetData>
@@ -3637,7 +3652,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3648,7 +3663,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -3667,7 +3682,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -3678,19 +3693,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C6" s="30"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C8" s="31" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -3699,7 +3714,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C9" s="31">
         <v>15</v>
@@ -3707,7 +3722,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('F5-1 Cut &amp; Splice'!$G$15:$G$46)&gt;=250*0.5,SUM('F5-2 Clean Up'!$G$15:$G$46)&gt;=250*0.5,SUM('F5-3 Find the Gem'!$G$13:$G$39)&gt;=200*0.5,SUM('F5-4 Assemble'!$G$13:$G$39)&gt;=200*0.5),"OPEN","LOCKED")</f>
@@ -3720,7 +3735,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3754,7 +3769,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B14" s="32" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which function joins a range of text with a delimiter?  (from F5-4 Assemble)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3777,7 +3792,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B15" s="32" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","Which function turns a number or date into formatted text?  (from F5-4 Assemble)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3800,7 +3815,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B16" s="32" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","Which function turns text that looks like a number into a number?  (from F5-4 Assemble)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3823,7 +3838,7 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="B17" s="32" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","Which function returns characters from the start of a text?  (from F5-1 Cut &amp; Splice)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3846,7 +3861,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B18" s="32" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","Which function returns characters from the end of a text?  (from F5-1 Cut &amp; Splice)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3869,7 +3884,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B19" s="32" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","Which function returns characters from the middle of a text?  (from F5-1 Cut &amp; Splice)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3892,7 +3907,7 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B20" s="32" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which function counts the characters in a text?  (from F5-1 Cut &amp; Splice)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3915,7 +3930,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B21" s="32" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which character joins pieces of text in a formula?  (from F5-1 Cut &amp; Splice)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3938,7 +3953,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -3949,7 +3964,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3977,14 +3992,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B26" s="32" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In D6 tidy B6: no extra spaces, each word capitalized.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$6),EXACT('Boss Arena'!$D$6,Key!$C$100)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"PROPER"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TRIM"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use PROPER and TRIM"))))),"LOCKED")</f>
@@ -4002,14 +4017,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="B27" s="32" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In D7 return the 4 digits in the middle of B7 (they start at character 4).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$7),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$7),'Boss Arena'!$D$7=Key!$C$101),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MID"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use MID"))))),"LOCKED")</f>
@@ -4027,17 +4042,17 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="B28" s="32" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In D8 return the username in B8 (everything before ""@"").","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
-        <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$8),EXACT('Boss Arena'!$D$8,Key!$C$102)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"LEFT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$8))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use LEFT and FIND"))))),"LOCKED")</f>
+        <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$8),EXACT('Boss Arena'!$D$8,Key!$C$102)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"LEFT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$8))))),OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$8))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SEARCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$8))))))),"✔ CLEAR","✘ CLOSE · right value, but use LEFT and FIND/SEARCH"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E28" s="22"/>
@@ -4052,17 +4067,17 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="B29" s="32" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In D9 return the last name from B9 (after the space).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
-        <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$9),EXACT('Boss Arena'!$D$9,Key!$C$103)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MID"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use MID and FIND"))))),"LOCKED")</f>
+        <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$9),EXACT('Boss Arena'!$D$9,Key!$C$103)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MID"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"RIGHT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$9)))))),OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SEARCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$9))))))),"✔ CLEAR","✘ CLOSE · right value, but use MID/RIGHT and FIND/SEARCH"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E29" s="22"/>
@@ -4077,14 +4092,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B30" s="32" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In D10 replace every ""/"" in B10 with ""-"".","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$10),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$10),'Boss Arena'!$D$10=Key!$C$104),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUBSTITUTE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$10)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUBSTITUTE"))))),"LOCKED")</f>
@@ -4102,14 +4117,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B31" s="32" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In D11 turn the text in B11 into a number.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$11),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$11)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$11),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$11),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$11),ABS('Boss Arena'!$D$11-Key!$C$105)&lt;=1E-9*MAX(1,ABS(Key!$C$105))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VALUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$11)))))),"✔ CLEAR","✘ CLOSE · right value, but use VALUE"))))),"LOCKED")</f>
@@ -4127,14 +4142,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="B32" s="32" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In D12 show the date in B12 as text like 04/07/2026 (format ""dd/mm/yyyy"").","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$12),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$12),'Boss Arena'!$D$12=Key!$C$106),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TEXT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$12)))))),"✔ CLEAR","✘ CLOSE · right value, but use TEXT"))))),"LOCKED")</f>
@@ -4152,14 +4167,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="B33" s="32" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In D13 join the tags in B15:B18 with "" | "", skipping the blank.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$D$13),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$13)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$D$13),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$D$13),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$D$13),EXACT('Boss Arena'!$D$13,Key!$C$107)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TEXTJOIN"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$13)))))),"✔ CLEAR","✘ CLOSE · right value, but use TEXTJOIN"))))),"LOCKED")</f>
@@ -4278,7 +4293,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4291,15 +4306,15 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="27" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>11</v>
@@ -4307,55 +4322,55 @@
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="5" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D6" s="28"/>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="5" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D7" s="28"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="5" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="5" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:4">
       <c r="B10" s="5" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D10" s="28"/>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="5" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D11" s="28"/>
     </row>
@@ -4364,34 +4379,34 @@
         <v>46207</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D12" s="28"/>
     </row>
     <row r="13" spans="1:4">
       <c r="C13" s="5" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D13" s="28"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="7" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="5" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="5" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="5" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
   </sheetData>
@@ -4419,7 +4434,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4427,245 +4442,245 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.75" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.75" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.75" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>39</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.75" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.75" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.75" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -4680,7 +4695,7 @@
   <dimension ref="A1:T107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4694,7 +4709,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -4720,7 +4735,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -4733,179 +4748,194 @@
       <c r="F3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="G3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
         <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
       </c>
       <c r="F9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G10" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H10" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
@@ -4917,24 +4947,24 @@
         <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H12" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B13" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F13" t="s">
         <v>30</v>
@@ -4943,15 +4973,15 @@
         <v>33</v>
       </c>
       <c r="H13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
@@ -4960,44 +4990,44 @@
         <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G14" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H14" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F15" t="s">
         <v>36</v>
       </c>
       <c r="G15" t="s">
+        <v>153</v>
+      </c>
+      <c r="H15" t="s">
         <v>148</v>
       </c>
-      <c r="H15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -5006,139 +5036,139 @@
         <v>39</v>
       </c>
       <c r="F16" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G16" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H16" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E17" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F17" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G17" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H17" t="s">
         <v>27</v>
       </c>
       <c r="I17" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J17" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E18" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F18" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G18" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H18" t="s">
         <v>30</v>
       </c>
       <c r="I18" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J18" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F19" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G19" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H19" t="s">
         <v>33</v>
       </c>
       <c r="I19" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J19" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E20" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F20" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G20" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H20" t="s">
         <v>36</v>
       </c>
       <c r="I20" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J20" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
         <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C22" cm="1" t="str">
         <f t="array" ref="C22">LEFT('F5-1 Arena'!$B$6,2)</f>
@@ -5147,10 +5177,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B23" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C23" cm="1" t="str">
         <f t="array" ref="C23">RIGHT('F5-1 Arena'!$B$6,1)</f>
@@ -5159,10 +5189,10 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B24" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C24" cm="1">
         <f t="array" ref="C24">MID('F5-1 Arena'!$B$6,4,4)</f>
@@ -5171,10 +5201,10 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B25" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C25" cm="1">
         <f t="array" ref="C25">LEN('F5-1 Arena'!$B$6)</f>
@@ -5183,10 +5213,10 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C26" cm="1" t="str">
         <f t="array" ref="C26">'F5-1 Arena'!$B$13&amp;" "&amp;'F5-1 Arena'!$C$13</f>
@@ -5195,485 +5225,518 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F27" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G27" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H27" t="s">
         <v>27</v>
       </c>
       <c r="I27" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J27" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E28" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F28" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G28" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H28" t="s">
         <v>30</v>
       </c>
       <c r="I28" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J28" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F29" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G29" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H29" t="s">
         <v>33</v>
       </c>
       <c r="I29" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J29" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E30" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F30" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G30" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H30" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J30" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>39</v>
       </c>
       <c r="F31" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B32" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E32" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F32" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G32" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H32" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I32" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="J32" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B33" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E33" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F33" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G33" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="H33" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I33" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="J33" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" t="s">
+        <v>268</v>
+      </c>
+      <c r="B34" t="s">
+        <v>269</v>
+      </c>
+      <c r="E34" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" t="s">
+      <c r="F34" t="s">
+        <v>262</v>
+      </c>
+      <c r="G34" t="s">
         <v>263</v>
       </c>
-      <c r="B34" t="s">
+      <c r="H34" t="s">
+        <v>270</v>
+      </c>
+      <c r="I34" t="s">
+        <v>271</v>
+      </c>
+      <c r="J34" t="s">
+        <v>272</v>
+      </c>
+      <c r="K34" t="s">
         <v>264</v>
       </c>
-      <c r="E34" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+      <c r="L34" t="s">
+        <v>265</v>
+      </c>
+      <c r="M34" t="s">
+        <v>266</v>
+      </c>
+      <c r="N34" t="s">
+        <v>273</v>
+      </c>
+      <c r="O34" t="s">
+        <v>274</v>
+      </c>
+      <c r="P34" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E35" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F35" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G35" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H35" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I35" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J35" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E36" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C37" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E37" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F37" t="s">
         <v>30</v>
       </c>
       <c r="G37" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E38" t="s">
         <v>33</v>
       </c>
       <c r="F38" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G38" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H38" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B39" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E39" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F39" t="s">
         <v>27</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H39" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B40" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E40" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F40" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G40" t="s">
         <v>33</v>
       </c>
       <c r="H40" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B41" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
         <v>30</v>
       </c>
       <c r="F41" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G41" t="s">
         <v>33</v>
       </c>
       <c r="H41" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B42" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E42" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F42" t="s">
+        <v>302</v>
+      </c>
+      <c r="G42" t="s">
+        <v>303</v>
+      </c>
+      <c r="H42" t="s">
+        <v>147</v>
+      </c>
+      <c r="I42" t="s">
+        <v>304</v>
+      </c>
+      <c r="J42" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" t="s">
+        <v>306</v>
+      </c>
+      <c r="B43" t="s">
+        <v>288</v>
+      </c>
+      <c r="E43" t="s">
+        <v>307</v>
+      </c>
+      <c r="F43" t="s">
+        <v>308</v>
+      </c>
+      <c r="G43" t="s">
+        <v>309</v>
+      </c>
+      <c r="H43" t="s">
+        <v>140</v>
+      </c>
+      <c r="I43" t="s">
+        <v>310</v>
+      </c>
+      <c r="J43" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" t="s">
+        <v>312</v>
+      </c>
+      <c r="B44" t="s">
+        <v>291</v>
+      </c>
+      <c r="E44" t="s">
+        <v>313</v>
+      </c>
+      <c r="F44" t="s">
+        <v>314</v>
+      </c>
+      <c r="G44" t="s">
+        <v>315</v>
+      </c>
+      <c r="H44" t="s">
+        <v>148</v>
+      </c>
+      <c r="I44" t="s">
+        <v>316</v>
+      </c>
+      <c r="J44" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" t="s">
+        <v>318</v>
+      </c>
+      <c r="B45" t="s">
+        <v>294</v>
+      </c>
+      <c r="E45" t="s">
+        <v>319</v>
+      </c>
+      <c r="F45" t="s">
+        <v>320</v>
+      </c>
+      <c r="G45" t="s">
+        <v>321</v>
+      </c>
+      <c r="H45" t="s">
+        <v>238</v>
+      </c>
+      <c r="I45" t="s">
+        <v>322</v>
+      </c>
+      <c r="J45" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" t="s">
+        <v>324</v>
+      </c>
+      <c r="B46" t="s">
         <v>297</v>
       </c>
-      <c r="G42" t="s">
-        <v>298</v>
-      </c>
-      <c r="H42" t="s">
-        <v>142</v>
-      </c>
-      <c r="I42" t="s">
-        <v>299</v>
-      </c>
-      <c r="J42" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" t="s">
-        <v>301</v>
-      </c>
-      <c r="B43" t="s">
-        <v>283</v>
-      </c>
-      <c r="E43" t="s">
-        <v>302</v>
-      </c>
-      <c r="F43" t="s">
-        <v>303</v>
-      </c>
-      <c r="G43" t="s">
-        <v>304</v>
-      </c>
-      <c r="H43" t="s">
-        <v>135</v>
-      </c>
-      <c r="I43" t="s">
-        <v>305</v>
-      </c>
-      <c r="J43" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" t="s">
-        <v>307</v>
-      </c>
-      <c r="B44" t="s">
-        <v>286</v>
-      </c>
-      <c r="E44" t="s">
-        <v>308</v>
-      </c>
-      <c r="F44" t="s">
-        <v>309</v>
-      </c>
-      <c r="G44" t="s">
-        <v>310</v>
-      </c>
-      <c r="H44" t="s">
-        <v>143</v>
-      </c>
-      <c r="I44" t="s">
-        <v>311</v>
-      </c>
-      <c r="J44" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" t="s">
-        <v>313</v>
-      </c>
-      <c r="B45" t="s">
-        <v>289</v>
-      </c>
-      <c r="E45" t="s">
-        <v>314</v>
-      </c>
-      <c r="F45" t="s">
-        <v>315</v>
-      </c>
-      <c r="G45" t="s">
-        <v>316</v>
-      </c>
-      <c r="H45" t="s">
-        <v>233</v>
-      </c>
-      <c r="I45" t="s">
-        <v>317</v>
-      </c>
-      <c r="J45" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" t="s">
-        <v>319</v>
-      </c>
-      <c r="B46" t="s">
-        <v>292</v>
-      </c>
       <c r="E46" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F46" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G46" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H46" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I46" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="J46" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C47" cm="1" t="str">
         <f t="array" ref="C47">TRIM('F5-2 Arena'!$B$6)</f>
         <v>ada LOVELACE</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C48" cm="1" t="str">
         <f t="array" ref="C48">UPPER('F5-2 Arena'!$B$7)</f>
@@ -5682,10 +5745,10 @@
     </row>
     <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B49" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C49" cm="1" t="str">
         <f t="array" ref="C49">LOWER('F5-2 Arena'!$B$8)</f>
@@ -5694,10 +5757,10 @@
     </row>
     <row r="50" spans="1:20">
       <c r="A50" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C50" cm="1" t="str">
         <f t="array" ref="C50">SUBSTITUTE('F5-2 Arena'!$B$9,"-","/")</f>
@@ -5706,10 +5769,10 @@
     </row>
     <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C51" cm="1" t="str">
         <f t="array" ref="C51">PROPER(TRIM('F5-2 Arena'!$B$6))</f>
@@ -5718,587 +5781,653 @@
     </row>
     <row r="52" spans="1:20">
       <c r="A52" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B52" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E52" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F52" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="G52" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="H52" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I52" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J52" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="53" spans="1:20">
       <c r="A53" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E53" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F53" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="G53" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="H53" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I53" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="J53" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="54" spans="1:20">
       <c r="A54" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B54" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E54" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F54" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="G54" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="H54" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I54" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J54" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:20">
       <c r="A55" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B55" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E55" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F55" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G55" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="H55" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I55" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="J55" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B56" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E56" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F56" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G56" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H56" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I56" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="J56" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B57" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E57" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B58" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E58" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F58" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="G58" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H58" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B59" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E59" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B60" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E60" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F60" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G60" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B61" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E61" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F61" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="G61" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="H61" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="I61" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="J61" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="K61" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="L61" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M61" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N61" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O61" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="P61" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Q61" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="R61" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="S61" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="T61" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B62" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E62" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F62" t="s">
         <v>27</v>
       </c>
       <c r="G62" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H62" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B63" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C63" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E63" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F63" t="s">
         <v>27</v>
       </c>
       <c r="G63" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H63" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B64" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C64" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E64" t="s">
         <v>39</v>
       </c>
       <c r="F64" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G64" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H64" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
       <c r="A65" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B65" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E65" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F65" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="G65" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="H65" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I65" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="J65" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
       <c r="A66" t="s">
+        <v>432</v>
+      </c>
+      <c r="B66" t="s">
+        <v>419</v>
+      </c>
+      <c r="E66" t="s">
+        <v>433</v>
+      </c>
+      <c r="F66" t="s">
+        <v>434</v>
+      </c>
+      <c r="G66" t="s">
+        <v>435</v>
+      </c>
+      <c r="H66" t="s">
+        <v>146</v>
+      </c>
+      <c r="I66" t="s">
+        <v>436</v>
+      </c>
+      <c r="J66" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" t="s">
+        <v>438</v>
+      </c>
+      <c r="B67" t="s">
+        <v>269</v>
+      </c>
+      <c r="E67" t="s">
         <v>427</v>
       </c>
-      <c r="B66" t="s">
-        <v>414</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="F67" t="s">
         <v>428</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G67" t="s">
         <v>429</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H67" t="s">
+        <v>433</v>
+      </c>
+      <c r="I67" t="s">
+        <v>434</v>
+      </c>
+      <c r="J67" t="s">
+        <v>435</v>
+      </c>
+      <c r="K67" t="s">
+        <v>134</v>
+      </c>
+      <c r="L67" t="s">
         <v>430</v>
       </c>
-      <c r="H66" t="s">
-        <v>141</v>
-      </c>
-      <c r="I66" t="s">
+      <c r="M67" t="s">
         <v>431</v>
       </c>
-      <c r="J66" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" t="s">
-        <v>433</v>
-      </c>
-      <c r="B67" t="s">
-        <v>264</v>
-      </c>
-      <c r="E67" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
+      <c r="N67" t="s">
+        <v>146</v>
+      </c>
+      <c r="O67" t="s">
+        <v>436</v>
+      </c>
+      <c r="P67" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
       <c r="A68" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B68" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C68" cm="1">
         <f t="array" ref="C68">FIND("@",'F5-3 Arena'!$B$6)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:16">
       <c r="A69" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B69" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C69" cm="1">
         <f t="array" ref="C69">SEARCH("ARCADE",'F5-3 Arena'!$B$6)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:16">
       <c r="A70" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B70" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C70" cm="1" t="str">
         <f t="array" ref="C70">LEFT('F5-3 Arena'!$B$6,FIND("@",'F5-3 Arena'!$B$6)-1)</f>
         <v>kim</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:16">
       <c r="A71" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B71" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C71" cm="1" t="str">
         <f t="array" ref="C71">MID('F5-3 Arena'!$B$7,FIND(" ",'F5-3 Arena'!$B$7)+1,100)</f>
         <v>Hopper</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:16">
       <c r="A72" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B72" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E72" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F72" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="G72" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="H72" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I72" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="J72" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
       <c r="A73" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B73" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E73" t="s">
+        <v>433</v>
+      </c>
+      <c r="F73" t="s">
+        <v>434</v>
+      </c>
+      <c r="G73" t="s">
+        <v>435</v>
+      </c>
+      <c r="H73" t="s">
+        <v>146</v>
+      </c>
+      <c r="I73" t="s">
+        <v>436</v>
+      </c>
+      <c r="J73" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
+      <c r="A74" t="s">
+        <v>482</v>
+      </c>
+      <c r="B74" t="s">
+        <v>269</v>
+      </c>
+      <c r="E74" t="s">
+        <v>427</v>
+      </c>
+      <c r="F74" t="s">
         <v>428</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G74" t="s">
         <v>429</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H74" t="s">
+        <v>433</v>
+      </c>
+      <c r="I74" t="s">
+        <v>434</v>
+      </c>
+      <c r="J74" t="s">
+        <v>435</v>
+      </c>
+      <c r="K74" t="s">
+        <v>134</v>
+      </c>
+      <c r="L74" t="s">
         <v>430</v>
       </c>
-      <c r="H73" t="s">
-        <v>141</v>
-      </c>
-      <c r="I73" t="s">
+      <c r="M74" t="s">
         <v>431</v>
       </c>
-      <c r="J73" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
-      <c r="A74" t="s">
-        <v>477</v>
-      </c>
-      <c r="B74" t="s">
-        <v>264</v>
-      </c>
-      <c r="E74" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+      <c r="N74" t="s">
+        <v>146</v>
+      </c>
+      <c r="O74" t="s">
+        <v>436</v>
+      </c>
+      <c r="P74" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
       <c r="A75" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B75" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E75" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
       <c r="A76" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B76" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="E76" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
       <c r="A77" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B77" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="E77" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
       <c r="A78" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B78" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E78" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
       <c r="A79" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B79" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="E79" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
       <c r="A80" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B80" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="E80" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B81" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="E81" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B82" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C82" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E82" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F82" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="G82" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H82" t="s">
         <v>36</v>
@@ -6306,22 +6435,22 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B83" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C83" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E83" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F83" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G83" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H83" t="s">
         <v>36</v>
@@ -6329,111 +6458,111 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B84" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C84" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E84" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F84" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G84" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H84" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B85" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="E85" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="F85" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="G85" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="H85" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I85" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J85" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B86" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="E86" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="F86" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="G86" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H86" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I86" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="J86" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B87" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E87" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="F87" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="G87" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H87" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="I87" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="J87" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B88" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C88" cm="1" t="str">
         <f t="array" ref="C88">_xlfn.TEXTJOIN(", ",TRUE,'F5-4 Arena'!$B$6:$B$10)</f>
@@ -6442,10 +6571,10 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B89" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C89" cm="1" t="str">
         <f t="array" ref="C89">TEXT('F5-4 Arena'!$B$12,"yyyy-mm-dd")</f>
@@ -6454,10 +6583,10 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B90" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C90" cm="1">
         <f t="array" ref="C90">VALUE('F5-4 Arena'!$B$14)</f>
@@ -6466,10 +6595,10 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B91" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C91" cm="1" t="str">
         <f t="array" ref="C91">"Total: "&amp;TEXT('F5-4 Arena'!$B$16,"$#,##0.00")</f>
@@ -6478,206 +6607,206 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B92" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="E92" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="F92" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="G92" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="H92" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I92" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J92" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B93" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="E93" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="F93" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="G93" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H93" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I93" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="J93" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="B94" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E94" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="F94" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="G94" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H94" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="I94" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="J94" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B95" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E95" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F95" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G95" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H95" t="s">
         <v>27</v>
       </c>
       <c r="I95" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J95" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B96" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E96" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F96" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G96" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H96" t="s">
         <v>30</v>
       </c>
       <c r="I96" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J96" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B97" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E97" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F97" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G97" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H97" t="s">
         <v>33</v>
       </c>
       <c r="I97" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J97" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B98" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E98" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F98" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G98" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H98" t="s">
         <v>36</v>
       </c>
       <c r="I98" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J98" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B99" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E99" t="s">
         <v>39</v>
       </c>
       <c r="F99" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B100" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C100" cm="1" t="str">
         <f t="array" ref="C100">PROPER(TRIM('Boss Arena'!$B$6))</f>
@@ -6686,10 +6815,10 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B101" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C101" cm="1">
         <f t="array" ref="C101">MID('Boss Arena'!$B$7,4,4)</f>
@@ -6698,10 +6827,10 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B102" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="C102" cm="1" t="str">
         <f t="array" ref="C102">LEFT('Boss Arena'!$B$8,FIND("@",'Boss Arena'!$B$8)-1)</f>
@@ -6710,10 +6839,10 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B103" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="C103" cm="1" t="str">
         <f t="array" ref="C103">MID('Boss Arena'!$B$9,FIND(" ",'Boss Arena'!$B$9)+1,100)</f>
@@ -6722,10 +6851,10 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B104" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="C104" cm="1" t="str">
         <f t="array" ref="C104">SUBSTITUTE('Boss Arena'!$B$10,"/","-")</f>
@@ -6734,10 +6863,10 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B105" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="C105" cm="1">
         <f t="array" ref="C105">VALUE('Boss Arena'!$B$11)</f>
@@ -6746,10 +6875,10 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="B106" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="C106" cm="1" t="str">
         <f t="array" ref="C106">TEXT('Boss Arena'!$B$12,"dd/mm/yyyy")</f>
@@ -6758,10 +6887,10 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B107" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C107" cm="1" t="str">
         <f t="array" ref="C107">_xlfn.TEXTJOIN(" | ",TRUE,'Boss Arena'!$B$15:$B$18)</f>
@@ -6793,7 +6922,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6804,7 +6933,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -6964,14 +7093,14 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
-        <f t="array" ref="D16">IFERROR(_xlfn.LET(_xlpm.a,'F5-1 Cut &amp; Splice'!$C$16,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$3:$F$3),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D16">IFERROR(_xlfn.LET(_xlpm.a,'F5-1 Cut &amp; Splice'!$C$16,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$3:$K$3),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E16" s="22"/>
@@ -6986,10 +7115,10 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -7008,10 +7137,10 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -7030,10 +7159,10 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -7052,10 +7181,10 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -7074,10 +7203,10 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -7096,10 +7225,10 @@
     </row>
     <row r="22" spans="1:7" ht="51.25" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -7118,10 +7247,10 @@
     </row>
     <row r="23" spans="1:7" ht="35.5" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -7140,10 +7269,10 @@
     </row>
     <row r="24" spans="1:7" ht="35.5" customHeight="1">
       <c r="A24" s="18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="21" cm="1" t="str">
@@ -7162,7 +7291,7 @@
     </row>
     <row r="26" spans="1:7" ht="22" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -7196,10 +7325,10 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -7218,10 +7347,10 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -7240,10 +7369,10 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -7262,10 +7391,10 @@
     </row>
     <row r="31" spans="1:7" ht="19.75" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -7284,10 +7413,10 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -7306,7 +7435,7 @@
     </row>
     <row r="34" spans="1:7" ht="22" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -7317,7 +7446,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="B35" s="11" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -7345,10 +7474,10 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -7367,10 +7496,10 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -7389,10 +7518,10 @@
     </row>
     <row r="39" spans="1:7" ht="35.5" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="21" cm="1" t="str">
@@ -7411,10 +7540,10 @@
     </row>
     <row r="40" spans="1:7" ht="19.75" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="21" cm="1" t="str">
@@ -7433,10 +7562,10 @@
     </row>
     <row r="41" spans="1:7" ht="35.5" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="21" cm="1" t="str">
@@ -7455,13 +7584,13 @@
     </row>
     <row r="42" spans="1:7" ht="35.5" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
         <f t="array" ref="D42">IF(ISBLANK('F5-1 Arena'!$E$6),"",IF(NOT(_xlfn.ISFORMULA('F5-1 Arena'!$E$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-1 Arena'!$E$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-1 Arena'!$E$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-1 Arena'!$E$6),EXACT('F5-1 Arena'!$E$6,Key!$C$22)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"LEFT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-1 Arena'!$E$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use LEFT")))))</f>
@@ -7479,13 +7608,13 @@
     </row>
     <row r="43" spans="1:7" ht="35.5" customHeight="1">
       <c r="A43" s="18" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D43" s="21" cm="1" t="str">
         <f t="array" ref="D43">IF(ISBLANK('F5-1 Arena'!$E$7),"",IF(NOT(_xlfn.ISFORMULA('F5-1 Arena'!$E$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-1 Arena'!$E$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-1 Arena'!$E$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-1 Arena'!$E$7),EXACT('F5-1 Arena'!$E$7,Key!$C$23)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"RIGHT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-1 Arena'!$E$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use RIGHT")))))</f>
@@ -7503,13 +7632,13 @@
     </row>
     <row r="44" spans="1:7" ht="35.5" customHeight="1">
       <c r="A44" s="18" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D44" s="21" cm="1" t="str">
         <f t="array" ref="D44">IF(ISBLANK('F5-1 Arena'!$E$8),"",IF(NOT(_xlfn.ISFORMULA('F5-1 Arena'!$E$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-1 Arena'!$E$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-1 Arena'!$E$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-1 Arena'!$E$8),EXACT('F5-1 Arena'!$E$8,Key!$C$24)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MID"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-1 Arena'!$E$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use MID")))))</f>
@@ -7527,13 +7656,13 @@
     </row>
     <row r="45" spans="1:7" ht="19.75" customHeight="1">
       <c r="A45" s="18" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D45" s="21" cm="1" t="str">
         <f t="array" ref="D45">IF(ISBLANK('F5-1 Arena'!$E$9),"",IF(NOT(_xlfn.ISFORMULA('F5-1 Arena'!$E$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-1 Arena'!$E$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-1 Arena'!$E$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F5-1 Arena'!$E$9),ABS('F5-1 Arena'!$E$9-Key!$C$25)&lt;=1E-9*MAX(1,ABS(Key!$C$25))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"LEN"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-1 Arena'!$E$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use LEN")))))</f>
@@ -7551,13 +7680,13 @@
     </row>
     <row r="46" spans="1:7" ht="35.5" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D46" s="21" cm="1" t="str">
         <f t="array" ref="D46">IF(ISBLANK('F5-1 Arena'!$E$13),"",IF(NOT(_xlfn.ISFORMULA('F5-1 Arena'!$E$13)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-1 Arena'!$E$13),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-1 Arena'!$E$13),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-1 Arena'!$E$13),EXACT('F5-1 Arena'!$E$13,Key!$C$26)),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("&amp;",_xlfn.FORMULATEXT('F5-1 Arena'!$E$13))),"✔ CLEAR","✘ CLOSE · your formula needs &amp;")))))</f>
@@ -7822,7 +7951,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7833,7 +7962,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -7885,10 +8014,10 @@
         <v>25</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="35.5" customHeight="1">
@@ -7896,10 +8025,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.5" customHeight="1">
@@ -7907,10 +8036,10 @@
         <v>31</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="35.5" customHeight="1">
@@ -7918,10 +8047,10 @@
         <v>34</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="67" customHeight="1">
@@ -7929,10 +8058,10 @@
         <v>37</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="22" customHeight="1">
@@ -7974,7 +8103,7 @@
         <v>54</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -7993,10 +8122,10 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -8015,10 +8144,10 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -8037,10 +8166,10 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -8059,10 +8188,10 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -8081,10 +8210,10 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -8103,10 +8232,10 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -8125,14 +8254,14 @@
     </row>
     <row r="22" spans="1:7" ht="35.5" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
-        <f t="array" ref="D22">IFERROR(_xlfn.LET(_xlpm.a,'F5-2 Clean Up'!$C$22,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$34:$E$34),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D22">IFERROR(_xlfn.LET(_xlpm.a,'F5-2 Clean Up'!$C$22,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$34:$P$34),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E22" s="22"/>
@@ -8147,10 +8276,10 @@
     </row>
     <row r="23" spans="1:7" ht="51.25" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -8169,10 +8298,10 @@
     </row>
     <row r="24" spans="1:7" ht="35.5" customHeight="1">
       <c r="A24" s="18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="21" cm="1" t="str">
@@ -8191,7 +8320,7 @@
     </row>
     <row r="26" spans="1:7" ht="22" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -8225,10 +8354,10 @@
     </row>
     <row r="28" spans="1:7" ht="19.75" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -8247,10 +8376,10 @@
     </row>
     <row r="29" spans="1:7" ht="19.75" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -8269,10 +8398,10 @@
     </row>
     <row r="30" spans="1:7" ht="19.75" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -8291,10 +8420,10 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -8313,10 +8442,10 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -8335,7 +8464,7 @@
     </row>
     <row r="34" spans="1:7" ht="22" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -8346,7 +8475,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="B35" s="11" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -8374,10 +8503,10 @@
     </row>
     <row r="37" spans="1:7" ht="19.75" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -8396,10 +8525,10 @@
     </row>
     <row r="38" spans="1:7" ht="19.75" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -8418,10 +8547,10 @@
     </row>
     <row r="39" spans="1:7" ht="19.75" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="21" cm="1" t="str">
@@ -8440,10 +8569,10 @@
     </row>
     <row r="40" spans="1:7" ht="35.5" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="21" cm="1" t="str">
@@ -8462,10 +8591,10 @@
     </row>
     <row r="41" spans="1:7" ht="35.5" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="21" cm="1" t="str">
@@ -8484,13 +8613,13 @@
     </row>
     <row r="42" spans="1:7" ht="35.5" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
         <f t="array" ref="D42">IF(ISBLANK('F5-2 Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('F5-2 Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-2 Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-2 Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-2 Arena'!$D$6),EXACT('F5-2 Arena'!$D$6,Key!$C$47)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TRIM"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-2 Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use TRIM")))))</f>
@@ -8508,13 +8637,13 @@
     </row>
     <row r="43" spans="1:7" ht="19.75" customHeight="1">
       <c r="A43" s="18" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D43" s="21" cm="1" t="str">
         <f t="array" ref="D43">IF(ISBLANK('F5-2 Arena'!$D$7),"",IF(NOT(_xlfn.ISFORMULA('F5-2 Arena'!$D$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-2 Arena'!$D$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-2 Arena'!$D$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-2 Arena'!$D$7),EXACT('F5-2 Arena'!$D$7,Key!$C$48)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UPPER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-2 Arena'!$D$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use UPPER")))))</f>
@@ -8532,13 +8661,13 @@
     </row>
     <row r="44" spans="1:7" ht="19.75" customHeight="1">
       <c r="A44" s="18" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D44" s="21" cm="1" t="str">
         <f t="array" ref="D44">IF(ISBLANK('F5-2 Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('F5-2 Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-2 Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-2 Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-2 Arena'!$D$8),EXACT('F5-2 Arena'!$D$8,Key!$C$49)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"LOWER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-2 Arena'!$D$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use LOWER")))))</f>
@@ -8556,13 +8685,13 @@
     </row>
     <row r="45" spans="1:7" ht="35.5" customHeight="1">
       <c r="A45" s="18" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D45" s="21" cm="1" t="str">
         <f t="array" ref="D45">IF(ISBLANK('F5-2 Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('F5-2 Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-2 Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-2 Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-2 Arena'!$D$9),'F5-2 Arena'!$D$9=Key!$C$50),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUBSTITUTE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-2 Arena'!$D$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUBSTITUTE")))))</f>
@@ -8580,13 +8709,13 @@
     </row>
     <row r="46" spans="1:7" ht="35.5" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D46" s="21" cm="1" t="str">
         <f t="array" ref="D46">IF(ISBLANK('F5-2 Arena'!$D$10),"",IF(NOT(_xlfn.ISFORMULA('F5-2 Arena'!$D$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-2 Arena'!$D$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-2 Arena'!$D$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-2 Arena'!$D$10),EXACT('F5-2 Arena'!$D$10,Key!$C$51)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"PROPER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-2 Arena'!$D$10))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TRIM"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-2 Arena'!$D$10)))))),"✔ CLEAR","✘ CLOSE · right value, but use PROPER and TRIM")))))</f>
@@ -8749,7 +8878,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -8762,15 +8891,15 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="27" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>11</v>
@@ -8778,43 +8907,43 @@
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D6" s="28"/>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="5" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D7" s="28"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="5" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:4">
       <c r="C10" s="5" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D10" s="28"/>
     </row>
@@ -8846,7 +8975,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8857,7 +8986,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8909,10 +9038,10 @@
         <v>25</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="67" customHeight="1">
@@ -8920,10 +9049,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="67" customHeight="1">
@@ -8931,10 +9060,10 @@
         <v>31</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22" customHeight="1">
@@ -8976,7 +9105,7 @@
         <v>54</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -8995,10 +9124,10 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -9017,10 +9146,10 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -9039,10 +9168,10 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -9061,10 +9190,10 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -9083,10 +9212,10 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -9105,10 +9234,10 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -9127,10 +9256,10 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -9149,10 +9278,10 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -9171,10 +9300,10 @@
     </row>
     <row r="22" spans="1:7" ht="35.5" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -9193,7 +9322,7 @@
     </row>
     <row r="24" spans="1:7" ht="22" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -9227,10 +9356,10 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -9249,10 +9378,10 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -9271,10 +9400,10 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -9293,7 +9422,7 @@
     </row>
     <row r="30" spans="1:7" ht="22" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -9304,7 +9433,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -9332,10 +9461,10 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -9354,10 +9483,10 @@
     </row>
     <row r="34" spans="1:7" ht="35.5" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -9376,14 +9505,14 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
-        <f t="array" ref="D35">IFERROR(_xlfn.LET(_xlpm.a,'F5-3 Find the Gem'!$C$35,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$67:$E$67),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D35">IFERROR(_xlfn.LET(_xlpm.a,'F5-3 Find the Gem'!$C$35,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$67:$P$67),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E35" s="22"/>
@@ -9398,13 +9527,13 @@
     </row>
     <row r="36" spans="1:7" ht="19.75" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F5-3 Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('F5-3 Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-3 Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-3 Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F5-3 Arena'!$D$6),ABS('F5-3 Arena'!$D$6-Key!$C$68)&lt;=1E-9*MAX(1,ABS(Key!$C$68))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use FIND")))))</f>
@@ -9422,13 +9551,13 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F5-3 Arena'!$D$7),"",IF(NOT(_xlfn.ISFORMULA('F5-3 Arena'!$D$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-3 Arena'!$D$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-3 Arena'!$D$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F5-3 Arena'!$D$7),ABS('F5-3 Arena'!$D$7-Key!$C$69)&lt;=1E-9*MAX(1,ABS(Key!$C$69))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SEARCH"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use SEARCH")))))</f>
@@ -9446,13 +9575,13 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F5-3 Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('F5-3 Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-3 Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-3 Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-3 Arena'!$D$8),EXACT('F5-3 Arena'!$D$8,Key!$C$70)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"LEFT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$8))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use LEFT and FIND")))))</f>
@@ -9470,13 +9599,13 @@
     </row>
     <row r="39" spans="1:7" ht="35.5" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F5-3 Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('F5-3 Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-3 Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-3 Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-3 Arena'!$D$9),EXACT('F5-3 Arena'!$D$9,Key!$C$71)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MID"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FIND"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-3 Arena'!$D$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use MID and FIND")))))</f>
@@ -9615,7 +9744,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -9628,15 +9757,15 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="27" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>11</v>
@@ -9644,31 +9773,31 @@
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="5" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D6" s="28"/>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="5" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D7" s="28"/>
     </row>
     <row r="8" spans="1:4">
       <c r="C8" s="5" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:4">
       <c r="C9" s="5" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D9" s="28"/>
     </row>
@@ -9700,7 +9829,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9711,7 +9840,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9763,10 +9892,10 @@
         <v>25</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="51.25" customHeight="1">
@@ -9774,10 +9903,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="67" customHeight="1">
@@ -9785,10 +9914,10 @@
         <v>31</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22" customHeight="1">
@@ -9830,7 +9959,7 @@
         <v>54</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -9849,10 +9978,10 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -9871,14 +10000,14 @@
     </row>
     <row r="15" spans="1:7" ht="51.25" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
-        <f t="array" ref="D15">IFERROR(_xlfn.LET(_xlpm.a,'F5-4 Assemble'!$C$15,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$74:$E$74),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D15">IFERROR(_xlfn.LET(_xlpm.a,'F5-4 Assemble'!$C$15,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$74:$P$74),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E15" s="22"/>
@@ -9893,10 +10022,10 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -9915,10 +10044,10 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -9937,10 +10066,10 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -9959,10 +10088,10 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -9981,10 +10110,10 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -10003,10 +10132,10 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -10025,10 +10154,10 @@
     </row>
     <row r="22" spans="1:7" ht="19.75" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -10047,7 +10176,7 @@
     </row>
     <row r="24" spans="1:7" ht="22" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -10081,10 +10210,10 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -10103,10 +10232,10 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -10125,10 +10254,10 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -10147,7 +10276,7 @@
     </row>
     <row r="30" spans="1:7" ht="22" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -10158,7 +10287,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -10186,10 +10315,10 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -10208,10 +10337,10 @@
     </row>
     <row r="34" spans="1:7" ht="35.5" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -10230,10 +10359,10 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -10252,13 +10381,13 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F5-4 Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('F5-4 Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-4 Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-4 Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-4 Arena'!$D$6),EXACT('F5-4 Arena'!$D$6,Key!$C$88)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TEXTJOIN"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-4 Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use TEXTJOIN")))))</f>
@@ -10276,13 +10405,13 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F5-4 Arena'!$D$12),"",IF(NOT(_xlfn.ISFORMULA('F5-4 Arena'!$D$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-4 Arena'!$D$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-4 Arena'!$D$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-4 Arena'!$D$12),'F5-4 Arena'!$D$12=Key!$C$89),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TEXT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-4 Arena'!$D$12)))))),"✔ CLEAR","✘ CLOSE · right value, but use TEXT")))))</f>
@@ -10300,13 +10429,13 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F5-4 Arena'!$D$14),"",IF(NOT(_xlfn.ISFORMULA('F5-4 Arena'!$D$14)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-4 Arena'!$D$14),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-4 Arena'!$D$14),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F5-4 Arena'!$D$14),ABS('F5-4 Arena'!$D$14-Key!$C$90)&lt;=1E-9*MAX(1,ABS(Key!$C$90))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"VALUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-4 Arena'!$D$14)))))),"✔ CLEAR","✘ CLOSE · right value, but use VALUE")))))</f>
@@ -10324,13 +10453,13 @@
     </row>
     <row r="39" spans="1:7" ht="35.5" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F5-4 Arena'!$D$16),"",IF(NOT(_xlfn.ISFORMULA('F5-4 Arena'!$D$16)),"✘ That's a typed value · enter a formula",IF(ISERROR('F5-4 Arena'!$D$16),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F5-4 Arena'!$D$16),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F5-4 Arena'!$D$16),EXACT('F5-4 Arena'!$D$16,Key!$C$91)),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"TEXT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F5-4 Arena'!$D$16)))))),"✔ CLEAR","✘ CLOSE · right value, but use TEXT")))))</f>
@@ -10468,7 +10597,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -10481,15 +10610,15 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="27" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>11</v>
@@ -10497,31 +10626,31 @@
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="5" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D6" s="28"/>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" s="5" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="5" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="B10" s="5" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="7" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -10529,27 +10658,27 @@
         <v>46096</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D12" s="28"/>
     </row>
     <row r="13" spans="1:4">
       <c r="B13" s="7" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="5" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D14" s="28"/>
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="7" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -10557,7 +10686,7 @@
         <v>1234.5</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D16" s="28"/>
     </row>
